--- a/LangMod/EN/LangGeneral.xlsx
+++ b/LangMod/EN/LangGeneral.xlsx
@@ -11,7 +11,7 @@
     <sheet name="General" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">General!$A$3:$D$44</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">General!$A$3:$D$47</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="136">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -385,6 +385,58 @@
   </si>
   <si>
     <t xml:space="preserve">Kill them until can retreat (#1 / #2)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">byakko_mod_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">progress_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">road_defence</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">敵対生物</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">を倒す (#1 / #2 体)</t>
+    </r>
   </si>
   <si>
     <r>
@@ -842,6 +894,36 @@
     <t xml:space="preserve">  &lt;color=#FFFF88&gt;Enemy Wave #1 Lv.#2&lt;/color&gt; (#3 of #4)</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">byakko_mod_status</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">_road</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_defence</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">qReward_byakko_mod_field_war</t>
   </si>
   <si>
@@ -849,6 +931,9 @@
   </si>
   <si>
     <t xml:space="preserve">#1 oren#(s) + Kill Bonus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">qReward_byakko_mod_road_defence</t>
   </si>
   <si>
     <t xml:space="preserve">qReward_byakko_mod_rescue</t>
@@ -1249,37 +1334,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18a303"/>
+        <a:srgbClr val="18A303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369a3"/>
+        <a:srgbClr val="0369A3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a33e03"/>
+        <a:srgbClr val="A33E03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8e03a3"/>
+        <a:srgbClr val="8E03A3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="c99c00"/>
+        <a:srgbClr val="C99C00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="c9211e"/>
+        <a:srgbClr val="C9211E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ee"/>
+        <a:srgbClr val="0000EE"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="0000ee"/>
+        <a:srgbClr val="0000EE"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Sheets">
@@ -1418,7 +1503,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:XFD44"/>
+  <dimension ref="A1:XFD47"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.29"/>
@@ -1798,281 +1883,358 @@
       <c r="B25" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C25" s="7" t="s">
         <v>72</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C26" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C26" s="1" t="s">
+      <c r="D26" s="1" t="s">
         <v>75</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C27" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C27" s="7" t="s">
+      <c r="D27" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D27" s="1" t="s">
+    </row>
+    <row r="28" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="8" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="28" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="8" t="s">
+      <c r="B28" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C28" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C28" s="6" t="s">
+      <c r="D28" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="D28" s="6" t="s">
+    </row>
+    <row r="29" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="8" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="29" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="9" t="s">
+      <c r="B29" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C29" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C29" s="6" t="s">
+      <c r="D29" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="D29" s="6" t="s">
+    </row>
+    <row r="30" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="9" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="30" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="8" t="s">
+      <c r="B30" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C30" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C30" s="6" t="s">
+      <c r="D30" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="D30" s="6" t="s">
+    </row>
+    <row r="31" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="8" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="31" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="10" t="s">
+      <c r="B31" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C31" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C31" s="11" t="s">
+      <c r="D31" s="6" t="s">
         <v>90</v>
-      </c>
-      <c r="D31" s="6" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="B32" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C32" s="11" t="s">
+      <c r="D32" s="6" t="s">
         <v>93</v>
-      </c>
-      <c r="D32" s="6" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C33" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="B33" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C33" s="11" t="s">
+      <c r="D33" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="D33" s="6" t="s">
+    </row>
+    <row r="34" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="10" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="34" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="8" t="s">
+      <c r="B34" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C34" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="B34" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C34" s="1" t="s">
+      <c r="D34" s="6" t="s">
         <v>99</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C35" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B35" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C35" s="1" t="s">
+      <c r="D35" s="1" t="s">
         <v>102</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C36" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="B36" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C36" s="1" t="s">
+      <c r="D36" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="D36" s="1" t="s">
+    </row>
+    <row r="37" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="8" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="37" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="12" t="s">
+      <c r="B37" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C37" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C37" s="13" t="s">
+      <c r="D37" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="D37" s="14" t="s">
+    </row>
+    <row r="38" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="8" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="38" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="12" t="s">
+      <c r="B38" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="XDV38" s="0"/>
+      <c r="XDW38" s="0"/>
+      <c r="XDX38" s="0"/>
+      <c r="XDY38" s="0"/>
+      <c r="XDZ38" s="0"/>
+      <c r="XEA38" s="0"/>
+      <c r="XEB38" s="0"/>
+      <c r="XEC38" s="0"/>
+      <c r="XED38" s="0"/>
+      <c r="XEE38" s="0"/>
+      <c r="XEF38" s="0"/>
+      <c r="XEG38" s="0"/>
+      <c r="XEH38" s="0"/>
+      <c r="XEI38" s="0"/>
+      <c r="XEJ38" s="0"/>
+      <c r="XEK38" s="0"/>
+      <c r="XEL38" s="0"/>
+      <c r="XEM38" s="0"/>
+      <c r="XEN38" s="0"/>
+      <c r="XEO38" s="0"/>
+      <c r="XEP38" s="0"/>
+      <c r="XEQ38" s="0"/>
+      <c r="XER38" s="0"/>
+      <c r="XES38" s="0"/>
+      <c r="XET38" s="0"/>
+      <c r="XEU38" s="0"/>
+      <c r="XEV38" s="0"/>
+      <c r="XEW38" s="0"/>
+      <c r="XEX38" s="0"/>
+      <c r="XEY38" s="0"/>
+      <c r="XEZ38" s="0"/>
+      <c r="XFA38" s="0"/>
+      <c r="XFB38" s="0"/>
+      <c r="XFC38" s="0"/>
+      <c r="XFD38" s="0"/>
+    </row>
+    <row r="39" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="B38" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C38" s="13" t="s">
+      <c r="B39" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="D38" s="14" t="s">
+      <c r="D39" s="14" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="5" t="s">
+    <row r="40" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="B39" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C39" s="13" t="s">
+      <c r="B40" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C40" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="D40" s="14" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="D39" s="14" t="s">
+      <c r="B41" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C41" s="13" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="40" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="6" t="s">
+      <c r="D41" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="B40" s="4" t="s">
+    </row>
+    <row r="42" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="C40" s="4" t="s">
+      <c r="B42" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C42" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="D40" s="15" t="s">
+      <c r="D42" s="14" t="s">
         <v>119</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="16" t="s">
-        <v>120</v>
-      </c>
-      <c r="B41" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="D41" s="15" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="16" t="s">
-        <v>123</v>
-      </c>
-      <c r="B42" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="C42" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="D42" s="15" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D43" s="15" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="16" t="s">
+        <v>124</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D44" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="B43" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="C43" s="4" t="s">
+    </row>
+    <row r="45" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="16" t="s">
         <v>127</v>
       </c>
-      <c r="D43" s="15" t="s">
+      <c r="B45" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C45" s="4" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="44" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="5" t="s">
+      <c r="D45" s="15" t="s">
         <v>129</v>
       </c>
-      <c r="B44" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="C44" s="4" t="s">
+    </row>
+    <row r="46" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="D44" s="15" t="s">
+      <c r="B46" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C46" s="4" t="s">
         <v>131</v>
       </c>
+      <c r="D46" s="15" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="D47" s="15" t="s">
+        <v>135</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:D44"/>
+  <autoFilter ref="A3:D47"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/LangMod/EN/LangGeneral.xlsx
+++ b/LangMod/EN/LangGeneral.xlsx
@@ -11,7 +11,7 @@
     <sheet name="General" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">General!$A$3:$D$47</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">General!$A$3:$D$61</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="178">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -158,6 +158,114 @@
     <t xml:space="preserve">The prey is not around here.</t>
   </si>
   <si>
+    <t xml:space="preserve">byakko_mod_music_mood_veryhigh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">最高！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Awesome!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">byakko_mod_music_mood_high</t>
+  </si>
+  <si>
+    <t xml:space="preserve">盛況</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Great</t>
+  </si>
+  <si>
+    <t xml:space="preserve">byakko_mod_music_mood_moderate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">いい感じ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Good</t>
+  </si>
+  <si>
+    <t xml:space="preserve">byakko_mod_music_mood_low</t>
+  </si>
+  <si>
+    <t xml:space="preserve">普通</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not bad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">byakko_mod_music_mood_annoy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">退屈</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bored</t>
+  </si>
+  <si>
+    <t xml:space="preserve">byakko_mod_music_mood_messed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">台無し</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buzzkilled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">byakko_mod_music_mood_fucked</t>
+  </si>
+  <si>
+    <t xml:space="preserve">最悪！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Messed!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">byakko_mod_music_party_end</t>
+  </si>
+  <si>
+    <t xml:space="preserve">パーティーが終了した。　</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The party has ended. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">byakko_mod_music_party_end_great</t>
+  </si>
+  <si>
+    <t xml:space="preserve">観客たちは大盛り上がりだ！　</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The audience is going wild! </t>
+  </si>
+  <si>
+    <t xml:space="preserve">byakko_mod_music_party_end_good</t>
+  </si>
+  <si>
+    <t xml:space="preserve">観客たちは満足したようだ。　</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The audience seemed satisfied. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">byakko_mod_music_party_end_worse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">雰囲気をぶち壊してやった！　</t>
+  </si>
+  <si>
+    <t xml:space="preserve">You totally ruined the mood! </t>
+  </si>
+  <si>
+    <t xml:space="preserve">byakko_mod_music_party_end_bad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">いまいちだった…　</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The audience is giving you cold stares. </t>
+  </si>
+  <si>
     <t xml:space="preserve">byakko_mod_progress_timer</t>
   </si>
   <si>
@@ -385,6 +493,42 @@
   </si>
   <si>
     <t xml:space="preserve">Kill them until can retreat (#1 / #2)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">byakko_mod_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">progress_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">music_monster</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">演奏し生き延びる (雰囲気:#1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Playing music to survive (Mood:#1)</t>
   </si>
   <si>
     <r>
@@ -922,6 +1066,61 @@
       </rPr>
       <t xml:space="preserve">_defence</t>
     </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">byakko_mod_status</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">_monster</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">_music</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">  &lt;color=#A5FFEF&gt;現在の雰囲気 : *#1*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">&lt;/color&gt;  </t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Current Mood : *#1*</t>
   </si>
   <si>
     <t xml:space="preserve">qReward_byakko_mod_field_war</t>
@@ -1134,6 +1333,13 @@
       <charset val="1"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <sz val="9.5"/>
       <color rgb="FF000000"/>
       <name val="游ゴシック"/>
@@ -1166,13 +1372,6 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="128"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="游ゴシック"/>
-      <family val="3"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1224,7 +1423,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1269,6 +1468,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1277,7 +1480,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1285,11 +1488,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1503,7 +1706,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:XFD47"/>
+  <dimension ref="A1:XFD61"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.29"/>
@@ -1722,519 +1925,715 @@
         <v>37</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="s">
+    <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="5" t="s">
         <v>38</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="5" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2" t="s">
+    <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="5" t="s">
         <v>41</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D15" s="5" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="s">
+    <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="5" t="s">
         <v>44</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D16" s="5" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2" t="s">
+    <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="5" t="s">
         <v>47</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D17" s="5" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2" t="s">
+    <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="5" t="s">
         <v>50</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="D18" s="5" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2" t="s">
+    <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="5" t="s">
         <v>53</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="D19" s="5" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2" t="s">
+    <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="5" t="s">
         <v>56</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="D20" s="7" t="s">
+      <c r="D20" s="5" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="2" t="s">
+    <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="5" t="s">
         <v>59</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="D21" s="7" t="s">
+      <c r="D21" s="5" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="2" t="s">
+    <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="5" t="s">
         <v>62</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="D22" s="7" t="s">
+      <c r="D22" s="5" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="8" t="s">
+    <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="5" t="s">
         <v>65</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C23" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="D23" s="5" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="8" t="s">
+    <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="5" t="s">
         <v>68</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C24" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="D24" s="5" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="8" t="s">
+    <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="5" t="s">
         <v>71</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C25" s="7" t="s">
+      <c r="C25" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="D25" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="8" t="s">
+      <c r="D25" s="5" t="s">
         <v>73</v>
       </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="2" t="s">
+        <v>74</v>
+      </c>
       <c r="B26" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C26" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="D26" s="1" t="s">
+      <c r="C26" s="2" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="27" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="8" t="s">
+      <c r="D26" s="2" t="s">
         <v>76</v>
       </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="2" t="s">
+        <v>77</v>
+      </c>
       <c r="B27" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C27" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="D27" s="1" t="s">
+      <c r="C27" s="2" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="28" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="8" t="s">
+      <c r="D27" s="2" t="s">
         <v>79</v>
       </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="2" t="s">
+        <v>80</v>
+      </c>
       <c r="B28" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C28" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="D28" s="1" t="s">
+      <c r="C28" s="2" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="29" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="8" t="s">
+      <c r="D28" s="2" t="s">
         <v>82</v>
       </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="2" t="s">
+        <v>83</v>
+      </c>
       <c r="B29" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C29" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="D29" s="6" t="s">
+      <c r="C29" s="2" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="30" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="9" t="s">
+      <c r="D29" s="2" t="s">
         <v>85</v>
       </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="2" t="s">
+        <v>86</v>
+      </c>
       <c r="B30" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C30" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="D30" s="6" t="s">
+      <c r="C30" s="2" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="31" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="8" t="s">
+      <c r="D30" s="2" t="s">
         <v>88</v>
       </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="2" t="s">
+        <v>89</v>
+      </c>
       <c r="B31" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C31" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="D31" s="6" t="s">
+      <c r="C31" s="2" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="32" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="10" t="s">
+      <c r="D31" s="7" t="s">
         <v>91</v>
       </c>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="2" t="s">
+        <v>92</v>
+      </c>
       <c r="B32" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C32" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="D32" s="6" t="s">
+      <c r="C32" s="2" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="33" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="10" t="s">
+      <c r="D32" s="7" t="s">
         <v>94</v>
       </c>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="2" t="s">
+        <v>95</v>
+      </c>
       <c r="B33" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C33" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="D33" s="6" t="s">
+      <c r="C33" s="2" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="34" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="10" t="s">
+      <c r="D33" s="7" t="s">
         <v>97</v>
       </c>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="2" t="s">
+        <v>98</v>
+      </c>
       <c r="B34" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C34" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="D34" s="6" t="s">
+      <c r="C34" s="2" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="35" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D34" s="7" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C37" s="1" t="s">
-        <v>107</v>
+      <c r="C37" s="9" t="s">
+        <v>108</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>108</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="XDV37" s="0"/>
+      <c r="XDW37" s="0"/>
+      <c r="XDX37" s="0"/>
+      <c r="XDY37" s="0"/>
+      <c r="XDZ37" s="0"/>
+      <c r="XEA37" s="0"/>
+      <c r="XEB37" s="0"/>
+      <c r="XEC37" s="0"/>
+      <c r="XED37" s="0"/>
+      <c r="XEE37" s="0"/>
+      <c r="XEF37" s="0"/>
+      <c r="XEG37" s="0"/>
+      <c r="XEH37" s="0"/>
+      <c r="XEI37" s="0"/>
+      <c r="XEJ37" s="0"/>
+      <c r="XEK37" s="0"/>
+      <c r="XEL37" s="0"/>
+      <c r="XEM37" s="0"/>
+      <c r="XEN37" s="0"/>
+      <c r="XEO37" s="0"/>
+      <c r="XEP37" s="0"/>
+      <c r="XEQ37" s="0"/>
+      <c r="XER37" s="0"/>
+      <c r="XES37" s="0"/>
+      <c r="XET37" s="0"/>
+      <c r="XEU37" s="0"/>
+      <c r="XEV37" s="0"/>
+      <c r="XEW37" s="0"/>
+      <c r="XEX37" s="0"/>
+      <c r="XEY37" s="0"/>
+      <c r="XEZ37" s="0"/>
+      <c r="XFA37" s="0"/>
+      <c r="XFB37" s="0"/>
+      <c r="XFC37" s="0"/>
+      <c r="XFD37" s="0"/>
     </row>
     <row r="38" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="8" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C38" s="1" t="s">
-        <v>107</v>
+      <c r="C38" s="7" t="s">
+        <v>111</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="XDV38" s="0"/>
-      <c r="XDW38" s="0"/>
-      <c r="XDX38" s="0"/>
-      <c r="XDY38" s="0"/>
-      <c r="XDZ38" s="0"/>
-      <c r="XEA38" s="0"/>
-      <c r="XEB38" s="0"/>
-      <c r="XEC38" s="0"/>
-      <c r="XED38" s="0"/>
-      <c r="XEE38" s="0"/>
-      <c r="XEF38" s="0"/>
-      <c r="XEG38" s="0"/>
-      <c r="XEH38" s="0"/>
-      <c r="XEI38" s="0"/>
-      <c r="XEJ38" s="0"/>
-      <c r="XEK38" s="0"/>
-      <c r="XEL38" s="0"/>
-      <c r="XEM38" s="0"/>
-      <c r="XEN38" s="0"/>
-      <c r="XEO38" s="0"/>
-      <c r="XEP38" s="0"/>
-      <c r="XEQ38" s="0"/>
-      <c r="XER38" s="0"/>
-      <c r="XES38" s="0"/>
-      <c r="XET38" s="0"/>
-      <c r="XEU38" s="0"/>
-      <c r="XEV38" s="0"/>
-      <c r="XEW38" s="0"/>
-      <c r="XEX38" s="0"/>
-      <c r="XEY38" s="0"/>
-      <c r="XEZ38" s="0"/>
-      <c r="XFA38" s="0"/>
-      <c r="XFB38" s="0"/>
-      <c r="XFC38" s="0"/>
-      <c r="XFD38" s="0"/>
+        <v>106</v>
+      </c>
     </row>
     <row r="39" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="12" t="s">
-        <v>110</v>
+      <c r="A39" s="8" t="s">
+        <v>112</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C39" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="D39" s="14" t="s">
-        <v>112</v>
+      <c r="C39" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="12" t="s">
-        <v>113</v>
+      <c r="A40" s="8" t="s">
+        <v>115</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C40" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="D40" s="14" t="s">
-        <v>112</v>
+      <c r="C40" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="12" t="s">
-        <v>114</v>
+      <c r="A41" s="8" t="s">
+        <v>118</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C41" s="13" t="s">
-        <v>115</v>
-      </c>
-      <c r="D41" s="14" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="5" t="s">
-        <v>117</v>
+      <c r="C41" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="8" t="s">
+        <v>121</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C42" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="D42" s="14" t="s">
-        <v>119</v>
+      <c r="C42" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="B43" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="C43" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="D43" s="15" t="s">
-        <v>123</v>
+      <c r="A43" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="16" t="s">
-        <v>124</v>
-      </c>
-      <c r="B44" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="C44" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="D44" s="15" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="16" t="s">
+      <c r="A44" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="B45" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="C45" s="4" t="s">
+      <c r="B44" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C44" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="D45" s="15" t="s">
+      <c r="D44" s="6" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="6" t="s">
+    <row r="45" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="B46" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="C46" s="4" t="s">
+      <c r="B45" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C45" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="D46" s="15" t="s">
+      <c r="D45" s="6" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="5" t="s">
+    <row r="46" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="B47" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="C47" s="4" t="s">
+      <c r="B46" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C46" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="D47" s="15" t="s">
+      <c r="D46" s="6" t="s">
         <v>135</v>
       </c>
     </row>
+    <row r="47" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C47" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C53" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="D53" s="15" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C54" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="D54" s="15" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C55" s="14" t="s">
+        <v>157</v>
+      </c>
+      <c r="D55" s="15" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C56" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="D56" s="15" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="D57" s="16" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="17" t="s">
+        <v>166</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="D58" s="16" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="17" t="s">
+        <v>169</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="D59" s="16" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="D60" s="16" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="D61" s="16" t="s">
+        <v>177</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:D47"/>
+  <autoFilter ref="A3:D61"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/LangMod/EN/LangGeneral.xlsx
+++ b/LangMod/EN/LangGeneral.xlsx
@@ -1120,7 +1120,36 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Current Mood : *#1*</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">  &lt;color=#A5FFEF&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Current Mood : *#1*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">&lt;/color&gt;  </t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">qReward_byakko_mod_field_war</t>
@@ -2260,41 +2289,6 @@
       <c r="D37" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="XDV37" s="0"/>
-      <c r="XDW37" s="0"/>
-      <c r="XDX37" s="0"/>
-      <c r="XDY37" s="0"/>
-      <c r="XDZ37" s="0"/>
-      <c r="XEA37" s="0"/>
-      <c r="XEB37" s="0"/>
-      <c r="XEC37" s="0"/>
-      <c r="XED37" s="0"/>
-      <c r="XEE37" s="0"/>
-      <c r="XEF37" s="0"/>
-      <c r="XEG37" s="0"/>
-      <c r="XEH37" s="0"/>
-      <c r="XEI37" s="0"/>
-      <c r="XEJ37" s="0"/>
-      <c r="XEK37" s="0"/>
-      <c r="XEL37" s="0"/>
-      <c r="XEM37" s="0"/>
-      <c r="XEN37" s="0"/>
-      <c r="XEO37" s="0"/>
-      <c r="XEP37" s="0"/>
-      <c r="XEQ37" s="0"/>
-      <c r="XER37" s="0"/>
-      <c r="XES37" s="0"/>
-      <c r="XET37" s="0"/>
-      <c r="XEU37" s="0"/>
-      <c r="XEV37" s="0"/>
-      <c r="XEW37" s="0"/>
-      <c r="XEX37" s="0"/>
-      <c r="XEY37" s="0"/>
-      <c r="XEZ37" s="0"/>
-      <c r="XFA37" s="0"/>
-      <c r="XFB37" s="0"/>
-      <c r="XFC37" s="0"/>
-      <c r="XFD37" s="0"/>
     </row>
     <row r="38" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="8" t="s">
@@ -2502,7 +2496,7 @@
       <c r="C52" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="D52" s="1" t="s">
+      <c r="D52" s="7" t="s">
         <v>151</v>
       </c>
     </row>
